--- a/artfynd/A 19934-2025 artfynd.xlsx
+++ b/artfynd/A 19934-2025 artfynd.xlsx
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
